--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kalyana\Gsheet Sprint 3\Traveloka_DataAutomation_Performer_Gsheet\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kalyana\Sprint 3 Gsheet\Traveloka_DataAutomation_Performer_Gsheet\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80A36D2-BC93-4C39-8E12-EF41E2E7C18B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ACCD5B-982B-4BBF-82A1-646D0904D662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="8964" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17268" windowHeight="8160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -177,12 +177,6 @@
     <t>GlobalVarAsset</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_UploadBucket</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_PathMailTemplate</t>
-  </si>
-  <si>
     <t>ConverterPath</t>
   </si>
   <si>
@@ -198,12 +192,6 @@
     <t>AutoRetryPostpone</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathExcel</t>
-  </si>
-  <si>
-    <t>[Dev] RPA_Moon_Cred_Gmail</t>
-  </si>
-  <si>
     <t>RPA_Moon_AutoRetryMaxDay</t>
   </si>
   <si>
@@ -216,22 +204,34 @@
     <t>AutoRetrySchedule</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_Gsheet</t>
-  </si>
-  <si>
     <t>PathSAKey</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_PathSaKey</t>
-  </si>
-  <si>
     <t>Gsheet_Raw_Data</t>
   </si>
   <si>
     <t>RawFolderName</t>
   </si>
   <si>
-    <t>[Dev] RPA_Moon_Gsheet_Date</t>
+    <t>RPA_Moon_PathMailTemplate</t>
+  </si>
+  <si>
+    <t>RPA_Moon_PathExcel</t>
+  </si>
+  <si>
+    <t>RPA_Moon_PathSaKey</t>
+  </si>
+  <si>
+    <t>RPA_Moon_Gsheet</t>
+  </si>
+  <si>
+    <t>RPA_Moon_Cred_Gmail</t>
+  </si>
+  <si>
+    <t>RPA_Moon_UploadBucket</t>
+  </si>
+  <si>
+    <t>RPA_Moon_Gsheet_Date</t>
   </si>
 </sst>
 </file>
@@ -311,9 +311,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -351,7 +351,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -457,7 +457,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -655,7 +655,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -687,7 +687,7 @@
         <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
@@ -695,7 +695,7 @@
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -708,10 +708,10 @@
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">
@@ -2926,7 +2926,7 @@
         <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
@@ -2939,50 +2939,50 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1">

--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kalyana\Sprint 3 Gsheet\Traveloka_DataAutomation_Performer_Gsheet\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6ACCD5B-982B-4BBF-82A1-646D0904D662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBA5907-580C-4C28-A770-D17C41D892E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17268" windowHeight="8160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -228,10 +228,10 @@
     <t>RPA_Moon_Cred_Gmail</t>
   </si>
   <si>
-    <t>RPA_Moon_UploadBucket</t>
-  </si>
-  <si>
     <t>RPA_Moon_Gsheet_Date</t>
+  </si>
+  <si>
+    <t>RPA_Moon_UploadBucket_2</t>
   </si>
 </sst>
 </file>
@@ -311,9 +311,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -351,7 +351,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -457,7 +457,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -599,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -695,7 +695,7 @@
         <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
@@ -703,7 +703,7 @@
         <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
@@ -2871,6 +2871,9 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="EpmWorksheetKeyString_GUID" r:id="rId1"/>
+  </customProperties>
 </worksheet>
 </file>
 
